--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CB822F-1DD1-4D7F-A735-FA296B2C7D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AB7F0A-A6B9-45B1-8D1F-A6163FA6F64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="47">
   <si>
     <t>日付</t>
   </si>
@@ -295,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -312,9 +312,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -964,7 +963,7 @@
       <c r="B3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>40569</v>
       </c>
       <c r="D3" s="7"/>
@@ -977,7 +976,7 @@
       <c r="B4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="9">
         <v>1048312</v>
       </c>
       <c r="D4" s="7"/>
@@ -990,7 +989,7 @@
       <c r="B5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="9">
         <v>129873</v>
       </c>
       <c r="D5" s="7"/>
@@ -1003,7 +1002,7 @@
       <c r="B6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>53216</v>
       </c>
       <c r="D6" s="7"/>
@@ -1016,7 +1015,7 @@
       <c r="B7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <v>107845</v>
       </c>
       <c r="D7" s="7"/>
@@ -1029,7 +1028,7 @@
       <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <v>19072</v>
       </c>
       <c r="D8" s="7"/>
@@ -1042,7 +1041,7 @@
       <c r="B9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="9">
         <v>42947</v>
       </c>
       <c r="D9" s="7"/>
@@ -1055,7 +1054,7 @@
       <c r="B10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="9">
         <v>151544</v>
       </c>
       <c r="D10" s="7"/>
@@ -1068,7 +1067,7 @@
       <c r="B11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <v>196431</v>
       </c>
       <c r="D11" s="7"/>
@@ -1081,7 +1080,7 @@
       <c r="B12" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <v>39537</v>
       </c>
       <c r="D12" s="7"/>
@@ -1094,7 +1093,7 @@
       <c r="B13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <v>38721</v>
       </c>
       <c r="D13" s="7"/>
@@ -1107,7 +1106,7 @@
       <c r="B14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>517093</v>
       </c>
       <c r="D14" s="7"/>
@@ -1120,7 +1119,7 @@
       <c r="B15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <v>63817</v>
       </c>
       <c r="D15" s="7"/>
@@ -1129,530 +1128,343 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="6"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="10"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="7"/>
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="6"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="10"/>
+      <c r="C17" s="9"/>
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="6"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="10"/>
+      <c r="C18" s="9"/>
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="6"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9"/>
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="6"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="10"/>
+      <c r="C20" s="9"/>
       <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="6"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9"/>
       <c r="D21" s="7"/>
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="6"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="10"/>
+      <c r="C22" s="9"/>
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="6"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9"/>
       <c r="D23" s="7"/>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="6"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="10"/>
+      <c r="C24" s="9"/>
       <c r="D24" s="7"/>
       <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="6"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9"/>
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="6"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="10"/>
+      <c r="C26" s="9"/>
       <c r="D26" s="7"/>
       <c r="E26" s="5"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="6"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9"/>
       <c r="D27" s="7"/>
       <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="6"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="10"/>
+      <c r="C28" s="9"/>
       <c r="D28" s="7"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9"/>
       <c r="D29" s="7"/>
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="10"/>
+      <c r="C30" s="9"/>
       <c r="D30" s="7"/>
       <c r="E30" s="5"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9"/>
       <c r="D31" s="7"/>
       <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
+      <c r="C32" s="9"/>
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="10"/>
+      <c r="C33" s="9"/>
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="10"/>
+      <c r="C34" s="9"/>
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A35" s="6">
-        <v>45901</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="10">
-        <v>265769</v>
-      </c>
+      <c r="A35" s="6"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="9"/>
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36" s="6">
-        <v>45902</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="10">
-        <v>77997</v>
-      </c>
+      <c r="A36" s="6"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="9"/>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="6">
-        <v>45903</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" s="10">
-        <v>1253405</v>
-      </c>
+      <c r="A37" s="6"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="9"/>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="6">
-        <v>45904</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="10">
-        <v>54795</v>
-      </c>
+      <c r="A38" s="6"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="9"/>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="6">
-        <v>45905</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="10">
-        <v>51215</v>
-      </c>
+      <c r="A39" s="6"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="9"/>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="6">
-        <v>45906</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="10">
-        <v>115925</v>
-      </c>
+      <c r="A40" s="6"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="9"/>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="6">
-        <v>45907</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="10">
-        <v>168411</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="9"/>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="6">
-        <v>45908</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="10">
-        <v>60678</v>
-      </c>
+      <c r="A42" s="6"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="9"/>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="6">
-        <v>45909</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="10">
-        <v>60042</v>
-      </c>
+      <c r="A43" s="6"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="9"/>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="6">
-        <v>45910</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" s="10">
-        <v>77156</v>
-      </c>
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="9"/>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="6">
-        <v>45911</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" s="10">
-        <v>60143</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="9"/>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="6">
-        <v>45912</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" s="10">
-        <v>88073</v>
-      </c>
+      <c r="A46" s="6"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="9"/>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="6">
-        <v>45913</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" s="10">
-        <v>940849</v>
-      </c>
+      <c r="A47" s="6"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="9"/>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="6">
-        <v>45914</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" s="10">
-        <v>39316</v>
-      </c>
+      <c r="A48" s="6"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="9"/>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="6">
-        <v>45915</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" s="10">
-        <v>55543</v>
-      </c>
+      <c r="A49" s="6"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="9"/>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="6">
-        <v>45916</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50" s="10">
-        <v>25837</v>
-      </c>
+      <c r="A50" s="6"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="9"/>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="6">
-        <v>45917</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" s="10">
-        <v>77745</v>
-      </c>
+      <c r="A51" s="6"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="9"/>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="6">
-        <v>45918</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" s="10">
-        <v>36561</v>
-      </c>
+      <c r="A52" s="6"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="9"/>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="6">
-        <v>45919</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" s="10">
-        <v>35011</v>
-      </c>
+      <c r="A53" s="6"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="9"/>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="6">
-        <v>45920</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C54" s="10">
-        <v>67247</v>
-      </c>
+      <c r="A54" s="6"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="9"/>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="6">
-        <v>45921</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="10">
-        <v>69864</v>
-      </c>
+      <c r="A55" s="6"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="9"/>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="6">
-        <v>45922</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="10">
-        <v>51374</v>
-      </c>
+      <c r="A56" s="6"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="9"/>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="6">
-        <v>45923</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C57" s="10">
-        <v>1277960</v>
-      </c>
+      <c r="A57" s="6"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="9"/>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="6">
-        <v>45924</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58" s="10">
-        <v>52313</v>
-      </c>
+      <c r="A58" s="6"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="9"/>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A59" s="6">
-        <v>45925</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C59" s="10">
-        <v>58758</v>
-      </c>
+      <c r="A59" s="6"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="9"/>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A60" s="6">
-        <v>45926</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60" s="10">
-        <v>40024</v>
-      </c>
+      <c r="A60" s="6"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="9"/>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="6">
-        <v>45927</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61" s="10">
-        <v>73994</v>
-      </c>
+      <c r="A61" s="6"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="9"/>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="6">
-        <v>45928</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C62" s="10">
-        <v>194805</v>
-      </c>
+      <c r="A62" s="6"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="9"/>
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A63" s="6">
-        <v>45929</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C63" s="10">
-        <v>45400</v>
-      </c>
+      <c r="A63" s="6"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="9"/>
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A64" s="6">
-        <v>45930</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C64" s="10">
-        <v>130737</v>
-      </c>
+      <c r="A64" s="6"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="9"/>
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="10"/>
+      <c r="C65" s="9"/>
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1721</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,30 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,6 +218,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -249,25 +242,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -279,16 +263,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,16 +285,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -332,16 +332,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +410,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,37 +452,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,43 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,25 +518,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,21 +581,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -606,15 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,6 +615,30 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1722"/>
+  <dimension ref="A1:E1723"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22942,8 +22942,19 @@
         <v>55417</v>
       </c>
     </row>
+    <row r="1723" spans="1:3">
+      <c r="A1723" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1723">
+        <v>53931</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1721">
+  <autoFilter ref="A1:E1722">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,9 +165,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -203,6 +203,30 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -210,9 +234,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,14 +243,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -242,14 +257,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,61 +301,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -334,7 +327,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +335,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,6 +362,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,7 +380,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +446,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,91 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,31 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +575,31 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,6 +619,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -606,50 +639,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +657,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1723"/>
+  <dimension ref="A1:E1724"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22953,8 +22953,19 @@
         <v>53931</v>
       </c>
     </row>
+    <row r="1724" spans="1:3">
+      <c r="A1724" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1724">
+        <v>249410</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1722">
+  <autoFilter ref="A1:E1723">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,69 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,22 +219,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,16 +273,70 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,25 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,13 +440,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,31 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,19 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +519,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,15 +575,62 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -604,21 +651,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -628,43 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1724"/>
+  <dimension ref="A1:E1725"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22964,8 +22964,19 @@
         <v>249410</v>
       </c>
     </row>
+    <row r="1725" spans="1:3">
+      <c r="A1725" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1725">
+        <v>307526</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1723">
+  <autoFilter ref="A1:E1724">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,7 +204,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,56 +256,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -286,45 +269,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -340,8 +291,57 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +404,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,37 +452,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +470,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,7 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,25 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -595,17 +586,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,11 +612,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +637,34 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1725"/>
+  <dimension ref="A1:E1726"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22975,8 +22975,19 @@
         <v>307526</v>
       </c>
     </row>
+    <row r="1726" spans="1:3">
+      <c r="A1726" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1726">
+        <v>53210</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1724">
+  <autoFilter ref="A1:E1725">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -203,8 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,6 +232,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -224,8 +254,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -240,65 +277,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -307,27 +285,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -340,8 +302,46 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,13 +386,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,19 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,43 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,25 +506,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -596,30 +614,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -630,15 +624,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,6 +639,21 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1726"/>
+  <dimension ref="A1:E1727"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22986,8 +22986,19 @@
         <v>53210</v>
       </c>
     </row>
+    <row r="1727" spans="1:3">
+      <c r="A1727" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1727">
+        <v>39976</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1725">
+  <autoFilter ref="A1:E1726">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,16 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,107 +219,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +234,114 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +386,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,97 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,13 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,7 +488,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,24 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -604,11 +586,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,6 +616,33 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -639,21 +654,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1727"/>
+  <dimension ref="A1:E1728"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -22997,8 +22997,19 @@
         <v>39976</v>
       </c>
     </row>
+    <row r="1728" spans="1:3">
+      <c r="A1728" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1728">
+        <v>499943</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1726">
+  <autoFilter ref="A1:E1727">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,62 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,8 +271,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,69 +333,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -305,45 +344,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +428,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +452,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,31 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,49 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -586,17 +595,28 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,37 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1728"/>
+  <dimension ref="A1:E1729"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23008,8 +23008,19 @@
         <v>499943</v>
       </c>
     </row>
+    <row r="1729" spans="1:3">
+      <c r="A1729" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1729">
+        <v>126586</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1727">
+  <autoFilter ref="A1:E1728">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -212,9 +219,31 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -227,7 +256,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,15 +272,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,33 +301,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,8 +316,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -321,29 +344,6 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,103 +368,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +392,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +416,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +446,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,13 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,9 +573,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,6 +593,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,11 +638,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,55 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1729"/>
+  <dimension ref="A1:E1730"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23019,8 +23019,19 @@
         <v>126586</v>
       </c>
     </row>
+    <row r="1730" spans="1:3">
+      <c r="A1730" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1730">
+        <v>229226</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1728">
+  <autoFilter ref="A1:E1729">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -204,22 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,29 +226,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,39 +242,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -326,6 +280,22 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -334,14 +304,44 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +404,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +458,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,103 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,13 +571,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -593,6 +612,35 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,61 +668,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,124 +695,124 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1730"/>
+  <dimension ref="A1:E1731"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23030,8 +23030,19 @@
         <v>229226</v>
       </c>
     </row>
+    <row r="1731" spans="1:3">
+      <c r="A1731" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1731">
+        <v>52373</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1729">
+  <autoFilter ref="A1:E1730">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,8 +165,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -203,6 +203,76 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -218,15 +288,37 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,22 +326,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,85 +340,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +386,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +410,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,25 +476,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,67 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,21 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -597,6 +582,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,13 +625,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -647,24 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1731"/>
+  <dimension ref="A1:E1732"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23041,8 +23041,19 @@
         <v>52373</v>
       </c>
     </row>
+    <row r="1732" spans="1:3">
+      <c r="A1732" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1732">
+        <v>63168</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1730">
+  <autoFilter ref="A1:E1731">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,9 +203,36 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,8 +246,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,6 +256,53 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -243,82 +318,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,15 +334,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +380,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,61 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +458,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,55 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,17 +610,37 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,180 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1732"/>
+  <dimension ref="A1:E1733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23052,8 +23052,19 @@
         <v>63168</v>
       </c>
     </row>
+    <row r="1733" spans="1:3">
+      <c r="A1733" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1733">
+        <v>42155</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1731">
+  <autoFilter ref="A1:E1732">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,51 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,7 +219,59 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -277,6 +285,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -285,9 +301,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,7 +310,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,33 +325,18 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +422,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +470,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,127 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,8 +574,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,6 +591,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,44 +627,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +648,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1733"/>
+  <dimension ref="A1:E1734"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23063,8 +23063,19 @@
         <v>42155</v>
       </c>
     </row>
+    <row r="1734" spans="1:3">
+      <c r="A1734" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1734">
+        <v>29797</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1732">
+  <autoFilter ref="A1:E1733">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1734</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,8 +165,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -204,7 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,59 +219,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,22 +235,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,10 +264,25 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -341,7 +303,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,175 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,17 +580,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,30 +604,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -645,6 +615,21 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,13 +653,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,49 +692,49 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -743,76 +743,76 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1734"/>
+  <dimension ref="A1:E1735"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23074,8 +23074,16 @@
         <v>29797</v>
       </c>
     </row>
+    <row r="1735" spans="1:2">
+      <c r="A1735" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1733">
+  <autoFilter ref="A1:E1734">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1735</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -205,7 +205,58 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -214,6 +265,29 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,52 +309,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,55 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,13 +368,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,31 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,25 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,55 +458,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,7 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,28 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,17 +595,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,11 +619,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,151 +657,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1736"/>
+  <dimension ref="A1:E1737"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23096,8 +23096,19 @@
         <v>141085</v>
       </c>
     </row>
+    <row r="1737" spans="1:3">
+      <c r="A1737" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1737">
+        <v>23176</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1735">
+  <autoFilter ref="A1:E1736">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,111 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -219,15 +324,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,106 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +380,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +458,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,13 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,43 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -513,36 +543,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,17 +619,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,15 +641,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +662,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1737"/>
+  <dimension ref="A1:E1738"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23107,8 +23107,19 @@
         <v>23176</v>
       </c>
     </row>
+    <row r="1738" spans="1:3">
+      <c r="A1738" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1738">
+        <v>303256</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1736">
+  <autoFilter ref="A1:E1737">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,52 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -256,37 +212,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,18 +235,69 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -332,11 +309,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -344,6 +328,22 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +386,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,145 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,45 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,6 +606,45 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1738"/>
+  <dimension ref="A1:E1739"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23118,8 +23118,19 @@
         <v>303256</v>
       </c>
     </row>
+    <row r="1739" spans="1:3">
+      <c r="A1739" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1739">
+        <v>42381</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1737">
+  <autoFilter ref="A1:E1738">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -212,41 +212,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -257,6 +232,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -272,6 +255,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -281,21 +280,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,25 +316,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -339,11 +340,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +380,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +434,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,19 +482,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,109 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -587,6 +593,30 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -609,38 +639,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,137 +695,137 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1739"/>
+  <dimension ref="A1:E1740"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23129,8 +23129,19 @@
         <v>42381</v>
       </c>
     </row>
+    <row r="1740" spans="1:3">
+      <c r="A1740" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1740">
+        <v>78004</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1738">
+  <autoFilter ref="A1:E1739">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,16 +203,55 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,14 +265,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,7 +273,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,24 +288,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,31 +302,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,15 +327,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,157 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -588,35 +588,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -632,15 +606,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +633,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1740"/>
+  <dimension ref="A1:E1741"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23140,8 +23140,19 @@
         <v>78004</v>
       </c>
     </row>
+    <row r="1741" spans="1:3">
+      <c r="A1741" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1741">
+        <v>36224</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1739">
+  <autoFilter ref="A1:E1740">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,22 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,17 +218,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,8 +233,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -266,14 +251,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,14 +264,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -302,11 +271,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -326,6 +294,22 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -333,8 +317,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +335,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,55 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,7 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +500,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,37 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,56 +596,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -668,22 +618,72 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1741"/>
+  <dimension ref="A1:E1742"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23151,8 +23151,19 @@
         <v>36224</v>
       </c>
     </row>
+    <row r="1742" spans="1:3">
+      <c r="A1742" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1742">
+        <v>40219</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1740">
+  <autoFilter ref="A1:E1741">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,31 +257,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,6 +265,22 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,8 +294,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,14 +325,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -301,33 +332,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -335,13 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +374,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +464,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,73 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,19 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,11 +586,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,24 +651,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,34 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -677,13 +677,13 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1742"/>
+  <dimension ref="A1:E1743"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23162,8 +23162,19 @@
         <v>40219</v>
       </c>
     </row>
+    <row r="1743" spans="1:3">
+      <c r="A1743" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1743">
+        <v>30077</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1741">
+  <autoFilter ref="A1:E1742">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,15 +204,44 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,8 +255,62 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,45 +333,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,52 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +416,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,55 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,13 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,45 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -619,17 +580,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,11 +615,56 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1743"/>
+  <dimension ref="A1:E1744"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23173,8 +23173,19 @@
         <v>30077</v>
       </c>
     </row>
+    <row r="1744" spans="1:3">
+      <c r="A1744" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1744">
+        <v>33150</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1742">
+  <autoFilter ref="A1:E1743">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,28 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -240,15 +218,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,16 +240,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -286,16 +271,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,22 +295,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,9 +309,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,109 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,37 +458,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,42 +575,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -632,24 +612,35 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +659,173 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1744"/>
+  <dimension ref="A1:E1745"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23184,8 +23184,19 @@
         <v>33150</v>
       </c>
     </row>
+    <row r="1745" spans="1:3">
+      <c r="A1745" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1745">
+        <v>41127</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1743">
+  <autoFilter ref="A1:E1744">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,45 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -218,10 +257,18 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -232,8 +279,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -247,47 +316,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,45 +333,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +458,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,103 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -595,17 +610,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,188 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1745"/>
+  <dimension ref="A1:E1746"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23195,8 +23195,19 @@
         <v>41127</v>
       </c>
     </row>
+    <row r="1746" spans="1:3">
+      <c r="A1746" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1746">
+        <v>96110</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1744">
+  <autoFilter ref="A1:E1745">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,129 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -346,6 +225,127 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,55 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,37 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +410,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +434,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,13 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -586,11 +597,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,6 +636,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -633,199 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1746"/>
+  <dimension ref="A1:E1747"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23206,8 +23206,19 @@
         <v>96110</v>
       </c>
     </row>
+    <row r="1747" spans="1:3">
+      <c r="A1747" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1747">
+        <v>30493</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1745">
+  <autoFilter ref="A1:E1746">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,52 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,70 +224,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +242,106 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,43 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +440,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,19 +488,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,49 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,21 +651,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -640,31 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,149 +683,149 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1747"/>
+  <dimension ref="A1:E1748"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23217,8 +23217,19 @@
         <v>30493</v>
       </c>
     </row>
+    <row r="1748" spans="1:3">
+      <c r="A1748" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1748">
+        <v>30493</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1746">
+  <autoFilter ref="A1:E1747">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,8 +164,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
@@ -203,6 +203,21 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -210,8 +225,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,19 +294,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -262,90 +346,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,55 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +392,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,67 +470,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,6 +506,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -543,6 +525,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,63 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -582,15 +639,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,70 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,124 +692,124 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1748"/>
+  <dimension ref="A1:E1749"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23228,8 +23228,19 @@
         <v>30493</v>
       </c>
     </row>
+    <row r="1749" spans="1:3">
+      <c r="A1749" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1749">
+        <v>256415</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1747">
+  <autoFilter ref="A1:E1748">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,14 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -219,40 +211,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -271,9 +255,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,24 +303,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -316,34 +324,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,175 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,8 +574,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,15 +606,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,9 +627,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,28 +651,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1749"/>
+  <dimension ref="A1:E1750"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23239,8 +23239,19 @@
         <v>256415</v>
       </c>
     </row>
+    <row r="1750" spans="1:3">
+      <c r="A1750" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1750">
+        <v>14296</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1748">
+  <autoFilter ref="A1:E1749">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -204,7 +204,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,18 +233,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -262,17 +279,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,21 +317,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -324,26 +332,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,13 +380,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +416,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +476,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,37 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,61 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,23 +574,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,6 +612,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -654,17 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1750"/>
+  <dimension ref="A1:E1751"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23250,8 +23250,19 @@
         <v>14296</v>
       </c>
     </row>
+    <row r="1751" spans="1:3">
+      <c r="A1751" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1751">
+        <v>74162</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1749">
+  <autoFilter ref="A1:E1750">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,6 +248,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -227,15 +318,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,97 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +392,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,19 +440,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +470,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,19 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,37 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,17 +616,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,28 +645,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,173 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1751"/>
+  <dimension ref="A1:E1752"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23261,8 +23261,19 @@
         <v>74162</v>
       </c>
     </row>
+    <row r="1752" spans="1:3">
+      <c r="A1752" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1752">
+        <v>71194</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1750">
+  <autoFilter ref="A1:E1751">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,30 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,23 +224,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,23 +240,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,7 +263,69 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,33 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,25 +428,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,73 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,43 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,16 +572,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,17 +601,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,8 +619,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,7 +640,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,23 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1752"/>
+  <dimension ref="A1:E1754"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23272,8 +23272,30 @@
         <v>71194</v>
       </c>
     </row>
+    <row r="1753" spans="1:3">
+      <c r="A1753" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1753">
+        <v>71194</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:3">
+      <c r="A1754" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1754">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1751">
+  <autoFilter ref="A1:E1753">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,14 +240,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,37 +248,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,6 +287,36 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -301,49 +332,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,13 +392,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +470,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,139 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,30 +610,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -632,15 +617,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +639,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1754"/>
+  <dimension ref="A1:E1755"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23294,8 +23294,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1755" spans="1:3">
+      <c r="A1755" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1755">
+        <v>117677</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1753">
+  <autoFilter ref="A1:E1754">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,8 +203,77 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,22 +287,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -246,16 +302,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,9 +317,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,36 +333,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -323,25 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +386,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,37 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +446,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,8 +574,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,6 +606,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,199 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1755"/>
+  <dimension ref="A1:E1756"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23305,8 +23305,19 @@
         <v>117677</v>
       </c>
     </row>
+    <row r="1756" spans="1:3">
+      <c r="A1756" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1756">
+        <v>50219</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1754">
+  <autoFilter ref="A1:E1755">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,8 +164,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
@@ -203,98 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -310,6 +218,22 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -318,7 +242,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,6 +294,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -340,10 +316,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +410,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,49 +452,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +482,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,43 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,21 +581,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -606,15 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,15 +606,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,13 +635,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1756"/>
+  <dimension ref="A1:E1757"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23316,8 +23316,19 @@
         <v>50219</v>
       </c>
     </row>
+    <row r="1757" spans="1:3">
+      <c r="A1757" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1757">
+        <v>42125</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1755">
+  <autoFilter ref="A1:E1756">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,15 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,9 +219,59 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,29 +286,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,37 +294,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,16 +308,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,10 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +386,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,49 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,31 +428,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,37 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,21 +582,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,11 +603,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,8 +613,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +637,34 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1757"/>
+  <dimension ref="A1:E1758"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23327,8 +23327,19 @@
         <v>42125</v>
       </c>
     </row>
+    <row r="1758" spans="1:3">
+      <c r="A1758" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1758">
+        <v>49233</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1756">
+  <autoFilter ref="A1:E1757">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,36 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -247,29 +217,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -286,7 +249,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,6 +258,20 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,7 +286,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -323,6 +316,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -331,17 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,55 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +398,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,13 +482,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,25 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,61 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,30 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,10 +619,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -657,175 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1758"/>
+  <dimension ref="A1:E1759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23338,8 +23338,19 @@
         <v>49233</v>
       </c>
     </row>
+    <row r="1759" spans="1:3">
+      <c r="A1759" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1759">
+        <v>56947</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1757">
+  <autoFilter ref="A1:E1758">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,14 +204,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,7 +248,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -233,15 +256,60 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -263,51 +331,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -316,32 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,61 +410,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +440,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +470,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,37 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -531,18 +543,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,9 +573,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,6 +593,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,41 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1759"/>
+  <dimension ref="A1:E1760"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23349,8 +23349,19 @@
         <v>56947</v>
       </c>
     </row>
+    <row r="1760" spans="1:3">
+      <c r="A1760" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1760">
+        <v>285310</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1758">
+  <autoFilter ref="A1:E1759">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,14 +203,73 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -227,21 +286,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,21 +308,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -279,14 +317,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,50 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +422,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,157 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,11 +573,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,30 +604,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -654,6 +628,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -668,22 +657,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1760"/>
+  <dimension ref="A1:E1762"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23360,8 +23360,30 @@
         <v>285310</v>
       </c>
     </row>
+    <row r="1761" spans="1:3">
+      <c r="A1761" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1761">
+        <v>285310</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:3">
+      <c r="A1762" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1762">
+        <v>43586</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1759">
+  <autoFilter ref="A1:E1761">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,17 +204,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -225,11 +226,57 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,9 +295,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -262,31 +317,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,50 +333,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,7 +368,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,49 +500,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,61 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,49 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +575,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,8 +598,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -607,8 +622,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,17 +643,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,17 +668,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -677,155 +677,155 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1762"/>
+  <dimension ref="A1:E1763"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23382,8 +23382,19 @@
         <v>43586</v>
       </c>
     </row>
+    <row r="1763" spans="1:3">
+      <c r="A1763" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1763">
+        <v>50731</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1761">
+  <autoFilter ref="A1:E1762">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,45 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -257,7 +218,53 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -266,7 +273,22 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,17 +302,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,47 +325,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +422,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,55 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,24 +573,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -629,27 +616,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +644,188 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1763"/>
+  <dimension ref="A1:E1764"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23393,8 +23393,19 @@
         <v>50731</v>
       </c>
     </row>
+    <row r="1764" spans="1:3">
+      <c r="A1764" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1764">
+        <v>46459</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1762">
+  <autoFilter ref="A1:E1763">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -217,26 +217,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,10 +232,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -279,11 +263,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -303,15 +295,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -326,17 +310,33 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,13 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +386,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,31 +404,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,31 +452,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,7 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,13 +500,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,22 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,22 +605,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -648,8 +628,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +648,184 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1764"/>
+  <dimension ref="A1:E1765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23404,8 +23404,19 @@
         <v>46459</v>
       </c>
     </row>
+    <row r="1765" spans="1:3">
+      <c r="A1765" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1765">
+        <v>70220</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1763">
+  <autoFilter ref="A1:E1764">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,6 +210,59 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -224,8 +277,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,46 +295,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -288,7 +310,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,41 +331,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +416,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,85 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,7 +476,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -582,6 +606,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,6 +630,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,208 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1765"/>
+  <dimension ref="A1:E1766"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23415,8 +23415,19 @@
         <v>70220</v>
       </c>
     </row>
+    <row r="1766" spans="1:3">
+      <c r="A1766" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1766">
+        <v>23146</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1764">
+  <autoFilter ref="A1:E1765">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -203,6 +203,51 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -211,8 +256,54 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,63 +324,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -302,48 +341,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +386,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,49 +500,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,79 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,26 +571,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,7 +614,33 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,35 +662,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1766"/>
+  <dimension ref="A1:E1767"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23426,8 +23426,19 @@
         <v>23146</v>
       </c>
     </row>
+    <row r="1767" spans="1:3">
+      <c r="A1767" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1767">
+        <v>42876</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1765">
+  <autoFilter ref="A1:E1766">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY2.xlsx
+++ b/dashboard/data/incoming/auPAY2.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1767</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -203,11 +203,33 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -218,45 +240,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -279,7 +264,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,9 +278,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,23 +300,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -333,7 +309,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -341,7 +317,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,30 +452,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -416,55 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,49 +476,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +494,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,22 +575,31 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,33 +623,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -662,9 +645,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1767"/>
+  <dimension ref="A1:E1768"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23437,8 +23437,19 @@
         <v>42876</v>
       </c>
     </row>
+    <row r="1768" spans="1:3">
+      <c r="A1768" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1768">
+        <v>59698</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1766">
+  <autoFilter ref="A1:E1767">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
